--- a/data/trans_dic/LAWTONB_2R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 33,12</t>
+          <t>9,74; 33,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 36,25</t>
+          <t>9,14; 34,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 20,18</t>
+          <t>4,16; 20,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 17,01</t>
+          <t>7,11; 16,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,37; 61,87</t>
+          <t>27,71; 62,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 31,7</t>
+          <t>4,09; 33,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,31; 46,83</t>
+          <t>11,14; 45,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 32,15</t>
+          <t>15,85; 31,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 38,23</t>
+          <t>19,45; 38,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 29,44</t>
+          <t>8,48; 29,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 24,32</t>
+          <t>8,64; 23,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 20,24</t>
+          <t>12,1; 20,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 36,57</t>
+          <t>12,3; 36,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 28,34</t>
+          <t>6,96; 28,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 31,06</t>
+          <t>11,53; 31,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 24,82</t>
+          <t>12,27; 24,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 62,14</t>
+          <t>13,19; 60,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,59; 70,37</t>
+          <t>23,84; 69,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,55; 74,51</t>
+          <t>19,81; 74,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,71; 40,61</t>
+          <t>21,68; 40,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 37,62</t>
+          <t>15,16; 38,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 34,93</t>
+          <t>13,4; 36,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 38,05</t>
+          <t>17,4; 38,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 26,94</t>
+          <t>17,01; 28,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 37,45</t>
+          <t>17,48; 37,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 31,52</t>
+          <t>14,75; 31,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 20,72</t>
+          <t>8,2; 20,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 26,08</t>
+          <t>13,94; 26,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 55,51</t>
+          <t>16,01; 55,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 48,63</t>
+          <t>22,28; 47,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,48; 52,3</t>
+          <t>21,51; 51,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,24; 50,99</t>
+          <t>31,74; 51,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,18; 37,33</t>
+          <t>20,21; 38,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 34,4</t>
+          <t>19,67; 33,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 26,23</t>
+          <t>13,65; 26,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,01; 32,03</t>
+          <t>21,91; 32,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 33,46</t>
+          <t>22,81; 33,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 36,46</t>
+          <t>22,85; 35,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 26,37</t>
+          <t>15,75; 26,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,41; 38,68</t>
+          <t>28,3; 38,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,54</t>
+          <t>20,3; 38,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,74; 52,32</t>
+          <t>27,44; 52,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 44,87</t>
+          <t>23,8; 45,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 33,08</t>
+          <t>2,93; 33,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 32,68</t>
+          <t>23,8; 33,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 38,01</t>
+          <t>26,61; 38,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,35; 30,65</t>
+          <t>20,34; 29,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 33,94</t>
+          <t>8,32; 34,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 43,79</t>
+          <t>20,06; 44,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,84; 44,85</t>
+          <t>26,0; 44,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 41,07</t>
+          <t>26,44; 41,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,2; 42,97</t>
+          <t>27,83; 43,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 48,48</t>
+          <t>27,59; 48,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,12; 52,34</t>
+          <t>37,95; 52,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 43,2</t>
+          <t>27,34; 43,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,43; 52,77</t>
+          <t>43,74; 53,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,76; 43,07</t>
+          <t>27,89; 43,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,71; 46,85</t>
+          <t>36,29; 48,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,91; 39,84</t>
+          <t>29,01; 39,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,25; 48,37</t>
+          <t>40,5; 48,71</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 75,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,83; 100,0</t>
+          <t>16,47; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,18; 38,48</t>
+          <t>29,66; 38,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,07; 42,22</t>
+          <t>32,03; 42,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,42; 41,84</t>
+          <t>31,88; 42,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,78; 49,76</t>
+          <t>41,68; 50,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,44; 38,64</t>
+          <t>29,12; 38,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,18; 42,13</t>
+          <t>31,97; 41,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,42; 41,84</t>
+          <t>31,88; 42,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,88; 49,87</t>
+          <t>42,3; 50,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,91; 30,11</t>
+          <t>22,57; 30,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,08; 31,0</t>
+          <t>22,81; 30,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,94; 24,15</t>
+          <t>17,87; 24,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,84; 28,3</t>
+          <t>23,06; 28,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,03</t>
+          <t>31,02; 38,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,74; 42,33</t>
+          <t>34,95; 42,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,9; 39,45</t>
+          <t>31,66; 39,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,51; 42,27</t>
+          <t>17,04; 42,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,19; 33,63</t>
+          <t>28,64; 33,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,82; 36,06</t>
+          <t>30,81; 36,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,59; 31,81</t>
+          <t>26,8; 32,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,65; 35,07</t>
+          <t>19,36; 35,06</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6122; 19799</t>
+          <t>5825; 19740</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3778; 15919</t>
+          <t>4014; 15217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3071; 13854</t>
+          <t>2855; 13759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8056; 18103</t>
+          <t>7569; 18062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8132; 18379</t>
+          <t>8231; 18524</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>993; 8017</t>
+          <t>1034; 8465</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4174; 17276</t>
+          <t>4109; 16815</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10515; 20999</t>
+          <t>10351; 20747</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16307; 34210</t>
+          <t>17405; 34755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6289; 20376</t>
+          <t>5867; 20399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9405; 25662</t>
+          <t>9123; 25242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20031; 34766</t>
+          <t>20787; 35111</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6102; 18587</t>
+          <t>6251; 18603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4092; 17184</t>
+          <t>4221; 17249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5576; 16570</t>
+          <t>6150; 16970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11323; 23576</t>
+          <t>11653; 23383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2148; 9810</t>
+          <t>2083; 9529</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4270; 13301</t>
+          <t>4507; 13161</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3614; 13105</t>
+          <t>3483; 13128</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10187; 19057</t>
+          <t>10175; 18954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10417; 25063</t>
+          <t>10096; 25426</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11185; 27783</t>
+          <t>10661; 28917</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12218; 26987</t>
+          <t>12342; 27148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23317; 38235</t>
+          <t>24145; 40037</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12605; 26870</t>
+          <t>12541; 26913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17159; 37404</t>
+          <t>17496; 37913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9884; 24918</t>
+          <t>9856; 25123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14275; 26465</t>
+          <t>14145; 26958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3756; 13476</t>
+          <t>3885; 13503</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12664; 26560</t>
+          <t>12171; 26189</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9927; 24168</t>
+          <t>9942; 23593</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16690; 26395</t>
+          <t>16433; 26455</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18421; 35848</t>
+          <t>19410; 36667</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34270; 59598</t>
+          <t>34085; 58603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22777; 43658</t>
+          <t>22725; 44369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32198; 49085</t>
+          <t>33579; 49368</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59438; 87031</t>
+          <t>59321; 86394</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55157; 84490</t>
+          <t>52947; 83109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31518; 53749</t>
+          <t>32098; 53713</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66967; 91174</t>
+          <t>66712; 90009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16069; 33049</t>
+          <t>17410; 32868</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16067; 31439</t>
+          <t>16493; 31339</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23872; 44441</t>
+          <t>23572; 45240</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9522; 108075</t>
+          <t>9568; 109422</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81115; 113018</t>
+          <t>82313; 114662</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78072; 110924</t>
+          <t>77670; 111034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61639; 92834</t>
+          <t>61597; 90562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45867; 190907</t>
+          <t>46793; 191239</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11182; 24288</t>
+          <t>11125; 24501</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26534; 46056</t>
+          <t>26705; 45735</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38166; 59646</t>
+          <t>38393; 60793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24597; 38863</t>
+          <t>25163; 39496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26327; 46667</t>
+          <t>26555; 46527</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71820; 98604</t>
+          <t>71493; 98188</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42528; 68921</t>
+          <t>43616; 69022</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88336; 107345</t>
+          <t>88972; 107913</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42123; 65348</t>
+          <t>42310; 66257</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103940; 136392</t>
+          <t>105637; 139804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88122; 121427</t>
+          <t>88420; 121748</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>118265; 142140</t>
+          <t>119006; 143123</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 2760</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>988; 3204</t>
+          <t>528; 3204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>124026; 163576</t>
+          <t>126094; 164526</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>126599; 166641</t>
+          <t>126425; 166912</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>129782; 172826</t>
+          <t>131704; 174469</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>133630; 159150</t>
+          <t>133301; 160185</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126215; 165674</t>
+          <t>124823; 165242</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127636; 167140</t>
+          <t>126816; 163998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129782; 172826</t>
+          <t>131704; 174469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>135291; 161111</t>
+          <t>136667; 162837</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114906; 151020</t>
+          <t>113200; 153236</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>129139; 173471</t>
+          <t>127667; 172407</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106103; 142797</t>
+          <t>105641; 143942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144382; 178926</t>
+          <t>145831; 180819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>207894; 257407</t>
+          <t>209951; 260274</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>257808; 314067</t>
+          <t>259328; 311950</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>246395; 304693</t>
+          <t>244556; 303683</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>187639; 428629</t>
+          <t>172775; 426451</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>332138; 396332</t>
+          <t>337533; 398705</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>401207; 469412</t>
+          <t>401087; 473420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>362576; 433744</t>
+          <t>365506; 441255</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>323424; 577291</t>
+          <t>318655; 577143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 33,02</t>
+          <t>9,9; 31,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 34,65</t>
+          <t>9,31; 37,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 20,04</t>
+          <t>4,75; 19,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,97</t>
+          <t>6,59; 16,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,71; 62,35</t>
+          <t>27,68; 63,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 33,47</t>
+          <t>3,98; 33,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 45,58</t>
+          <t>12,18; 45,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 31,76</t>
+          <t>15,26; 30,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 38,84</t>
+          <t>19,36; 38,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,48; 29,48</t>
+          <t>8,27; 29,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 23,92</t>
+          <t>8,73; 24,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 20,44</t>
+          <t>11,44; 19,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 36,6</t>
+          <t>12,55; 38,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 28,45</t>
+          <t>7,17; 29,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 31,81</t>
+          <t>11,59; 32,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 24,61</t>
+          <t>11,48; 24,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 60,36</t>
+          <t>13,37; 60,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 69,63</t>
+          <t>21,51; 70,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,81; 74,64</t>
+          <t>19,89; 73,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 40,39</t>
+          <t>21,24; 39,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 38,17</t>
+          <t>16,01; 37,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 36,36</t>
+          <t>14,17; 35,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,4; 38,27</t>
+          <t>16,74; 37,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 28,21</t>
+          <t>16,71; 26,75</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 37,51</t>
+          <t>17,93; 37,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 31,95</t>
+          <t>14,62; 32,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 20,89</t>
+          <t>8,61; 20,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,94; 26,56</t>
+          <t>13,47; 25,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,01; 55,62</t>
+          <t>17,04; 55,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,28; 47,95</t>
+          <t>23,34; 50,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 51,06</t>
+          <t>20,24; 51,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 51,1</t>
+          <t>33,12; 52,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,21; 38,18</t>
+          <t>20,33; 37,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,67; 33,82</t>
+          <t>19,44; 33,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 26,65</t>
+          <t>14,34; 26,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,91; 32,21</t>
+          <t>21,35; 32,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,81; 33,22</t>
+          <t>23,07; 33,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 35,86</t>
+          <t>24,1; 37,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 26,35</t>
+          <t>14,78; 25,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,3; 38,18</t>
+          <t>27,7; 37,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,3; 38,33</t>
+          <t>20,14; 39,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 52,15</t>
+          <t>28,02; 53,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 45,68</t>
+          <t>24,99; 46,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 33,49</t>
+          <t>26,58; 37,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 33,16</t>
+          <t>23,17; 32,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 38,05</t>
+          <t>26,45; 37,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,34; 29,9</t>
+          <t>19,49; 30,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 34,0</t>
+          <t>28,54; 36,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,06; 44,17</t>
+          <t>19,55; 42,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,0; 44,53</t>
+          <t>25,22; 44,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,44; 41,86</t>
+          <t>26,44; 41,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,83; 43,68</t>
+          <t>26,97; 43,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,59; 48,34</t>
+          <t>27,84; 48,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,95; 52,12</t>
+          <t>37,7; 52,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 43,26</t>
+          <t>26,71; 43,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 53,05</t>
+          <t>43,97; 53,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,89; 43,67</t>
+          <t>27,24; 43,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,29; 48,03</t>
+          <t>35,35; 47,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,01; 39,95</t>
+          <t>28,46; 39,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,5; 48,71</t>
+          <t>40,16; 48,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,71</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,47; 100,0</t>
+          <t>18,92; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,66; 38,71</t>
+          <t>29,4; 38,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,03; 42,29</t>
+          <t>32,74; 41,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,88; 42,24</t>
+          <t>31,18; 41,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,68; 50,08</t>
+          <t>42,16; 50,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,12; 38,54</t>
+          <t>29,33; 39,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,97; 41,34</t>
+          <t>32,2; 41,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,88; 42,24</t>
+          <t>31,18; 41,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 50,41</t>
+          <t>42,4; 50,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,57; 30,55</t>
+          <t>22,66; 30,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,81</t>
+          <t>22,85; 30,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,34</t>
+          <t>17,9; 24,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,06; 28,6</t>
+          <t>22,23; 27,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,45</t>
+          <t>30,92; 38,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,95; 42,04</t>
+          <t>34,54; 41,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,66; 39,32</t>
+          <t>31,74; 39,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 42,06</t>
+          <t>38,87; 43,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,64; 33,83</t>
+          <t>28,57; 33,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,81; 36,37</t>
+          <t>30,76; 36,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,8; 32,36</t>
+          <t>26,72; 31,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,36; 35,06</t>
+          <t>32,17; 35,87</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>29052</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5825; 19740</t>
+          <t>5921; 18637</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4014; 15217</t>
+          <t>4089; 16550</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2855; 13759</t>
+          <t>3259; 13460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7569; 18062</t>
+          <t>7860; 19723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8231; 18524</t>
+          <t>8223; 18807</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1034; 8465</t>
+          <t>1007; 8358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4109; 16815</t>
+          <t>4492; 16665</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10351; 20747</t>
+          <t>11380; 23028</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17405; 34755</t>
+          <t>17329; 34792</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5867; 20399</t>
+          <t>5724; 20205</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9123; 25242</t>
+          <t>9210; 26245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20787; 35111</t>
+          <t>22162; 38040</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>34250</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6251; 18603</t>
+          <t>6377; 19682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4221; 17249</t>
+          <t>4344; 18078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6150; 16970</t>
+          <t>6181; 17392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11653; 23383</t>
+          <t>12022; 25394</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2083; 9529</t>
+          <t>2110; 9561</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4507; 13161</t>
+          <t>4067; 13406</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3483; 13128</t>
+          <t>3499; 12884</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10175; 18954</t>
+          <t>11766; 21893</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10096; 25426</t>
+          <t>10667; 24925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10661; 28917</t>
+          <t>11272; 27862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12342; 27148</t>
+          <t>11873; 26264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24145; 40037</t>
+          <t>26754; 42819</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>45384</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12541; 26913</t>
+          <t>12865; 26786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17496; 37913</t>
+          <t>17343; 38649</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9856; 25123</t>
+          <t>10354; 24488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14145; 26958</t>
+          <t>15069; 28366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3885; 13503</t>
+          <t>4138; 13543</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12171; 26189</t>
+          <t>12747; 27447</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9942; 23593</t>
+          <t>9352; 23810</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16433; 26455</t>
+          <t>18859; 29702</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19410; 36667</t>
+          <t>19520; 36317</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34085; 58603</t>
+          <t>33685; 58737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22725; 44369</t>
+          <t>23867; 44322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33579; 49368</t>
+          <t>36046; 54423</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>84332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>117448</t>
+          <t>126048</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59321; 86394</t>
+          <t>60010; 87729</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52947; 83109</t>
+          <t>55853; 85799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32098; 53713</t>
+          <t>30137; 52776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66712; 90009</t>
+          <t>71276; 96786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17410; 32868</t>
+          <t>17269; 33466</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16493; 31339</t>
+          <t>16836; 32014</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23572; 45240</t>
+          <t>24756; 46432</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9568; 109422</t>
+          <t>34784; 49056</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82313; 114662</t>
+          <t>80124; 111093</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77670; 111034</t>
+          <t>77187; 109247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61597; 90562</t>
+          <t>59022; 90906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46793; 191239</t>
+          <t>110790; 141060</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>98262</t>
+          <t>106112</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>129680</t>
+          <t>140407</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11125; 24501</t>
+          <t>10845; 23334</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26705; 45735</t>
+          <t>25899; 45818</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38393; 60793</t>
+          <t>38389; 59891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25163; 39496</t>
+          <t>26711; 42908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26555; 46527</t>
+          <t>26797; 46932</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71493; 98188</t>
+          <t>71026; 98311</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43616; 69022</t>
+          <t>42613; 68808</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88972; 107913</t>
+          <t>95970; 116516</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42310; 66257</t>
+          <t>41328; 65336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105637; 139804</t>
+          <t>102899; 138450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88420; 121748</t>
+          <t>86731; 121384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>119006; 143123</t>
+          <t>127431; 153035</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>158279</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>148985</t>
+          <t>160483</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2760</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>528; 3204</t>
+          <t>620; 3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>126094; 164526</t>
+          <t>124989; 165016</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>126425; 166912</t>
+          <t>129224; 165631</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>131704; 174469</t>
+          <t>128820; 172657</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>133301; 160185</t>
+          <t>144891; 172297</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124823; 165242</t>
+          <t>125737; 168594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>126816; 163998</t>
+          <t>127749; 166583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131704; 174469</t>
+          <t>128820; 172657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136667; 162837</t>
+          <t>147093; 174521</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160818</t>
+          <t>172610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>334785</t>
+          <t>363015</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>495602</t>
+          <t>535625</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113200; 153236</t>
+          <t>113675; 152766</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>127667; 172407</t>
+          <t>127896; 172620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>105641; 143942</t>
+          <t>105867; 143017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145831; 180819</t>
+          <t>154620; 191081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>209951; 260274</t>
+          <t>209277; 259970</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>259328; 311950</t>
+          <t>256285; 311567</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>244556; 303683</t>
+          <t>245150; 302187</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>172775; 426451</t>
+          <t>341948; 385651</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337533; 398705</t>
+          <t>336683; 397482</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>401087; 473420</t>
+          <t>400432; 470148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>365506; 441255</t>
+          <t>364337; 434646</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>318655; 577143</t>
+          <t>506797; 564967</t>
         </is>
       </c>
     </row>
